--- a/artfynd/A 34085-2020 artfynd.xlsx
+++ b/artfynd/A 34085-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34085-2020 artfynd.xlsx
+++ b/artfynd/A 34085-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2399,6 +2399,347 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120338983</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>580308</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7056157</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120338909</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>580295</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7056158</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120338884</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>580269</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7056177</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34085-2020 artfynd.xlsx
+++ b/artfynd/A 34085-2020 artfynd.xlsx
@@ -2401,7 +2401,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120338983</v>
+        <v>120338909</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580308</v>
+        <v>580295</v>
       </c>
       <c r="R17" t="n">
-        <v>7056157</v>
+        <v>7056158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120338909</v>
+        <v>120338983</v>
       </c>
       <c r="B18" t="n">
         <v>79623</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580295</v>
+        <v>580308</v>
       </c>
       <c r="R18" t="n">
-        <v>7056158</v>
+        <v>7056157</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 34085-2020 artfynd.xlsx
+++ b/artfynd/A 34085-2020 artfynd.xlsx
@@ -2401,7 +2401,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120338909</v>
+        <v>120338983</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580295</v>
+        <v>580308</v>
       </c>
       <c r="R17" t="n">
-        <v>7056158</v>
+        <v>7056157</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120338983</v>
+        <v>120338884</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580308</v>
+        <v>580269</v>
       </c>
       <c r="R18" t="n">
-        <v>7056157</v>
+        <v>7056177</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2598,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,22 +2618,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120338884</v>
+        <v>120338909</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,34 +2646,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580269</v>
+        <v>580295</v>
       </c>
       <c r="R19" t="n">
-        <v>7056177</v>
+        <v>7056158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,12 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,12 +2730,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 34085-2020 artfynd.xlsx
+++ b/artfynd/A 34085-2020 artfynd.xlsx
@@ -2401,7 +2401,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120338983</v>
+        <v>120338909</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580308</v>
+        <v>580295</v>
       </c>
       <c r="R17" t="n">
-        <v>7056157</v>
+        <v>7056158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2630,7 +2630,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120338909</v>
+        <v>120338983</v>
       </c>
       <c r="B19" t="n">
         <v>79623</v>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580295</v>
+        <v>580308</v>
       </c>
       <c r="R19" t="n">
-        <v>7056158</v>
+        <v>7056157</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 34085-2020 artfynd.xlsx
+++ b/artfynd/A 34085-2020 artfynd.xlsx
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120338909</v>
+        <v>120338884</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580295</v>
+        <v>580269</v>
       </c>
       <c r="R17" t="n">
-        <v>7056158</v>
+        <v>7056177</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2486,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,22 +2506,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120338884</v>
+        <v>120338909</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,34 +2534,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580269</v>
+        <v>580295</v>
       </c>
       <c r="R18" t="n">
-        <v>7056177</v>
+        <v>7056158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,12 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,12 +2618,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 34085-2020 artfynd.xlsx
+++ b/artfynd/A 34085-2020 artfynd.xlsx
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120338884</v>
+        <v>120338909</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580269</v>
+        <v>580295</v>
       </c>
       <c r="R17" t="n">
-        <v>7056177</v>
+        <v>7056158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,12 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,22 +2501,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120338909</v>
+        <v>120338884</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2534,34 +2529,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580295</v>
+        <v>580269</v>
       </c>
       <c r="R18" t="n">
-        <v>7056158</v>
+        <v>7056177</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2598,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,12 +2618,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 34085-2020 artfynd.xlsx
+++ b/artfynd/A 34085-2020 artfynd.xlsx
@@ -2513,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120338884</v>
+        <v>120338983</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580269</v>
+        <v>580308</v>
       </c>
       <c r="R18" t="n">
-        <v>7056177</v>
+        <v>7056157</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,12 +2598,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,22 +2613,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120338983</v>
+        <v>120338884</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,34 +2641,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580308</v>
+        <v>580269</v>
       </c>
       <c r="R19" t="n">
-        <v>7056157</v>
+        <v>7056177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2710,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,12 +2730,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
